--- a/examples/customer-sync/规则_决策表.xlsx
+++ b/examples/customer-sync/规则_决策表.xlsx
@@ -669,7 +669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -749,11 +749,24 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>可用函数</t>
+          <t>连接词</t>
         </is>
       </c>
       <c r="B6" s="3" t="n"/>
       <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>且 / 或 / 非 (也认 and / or / not), 两侧留空格; 可用括号分组</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>可用函数</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n"/>
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>abs  round  天数差(晚, 早)  非空(x)  为空(x)  属于(x, 值1, 值2, ...)</t>
         </is>
@@ -803,7 +816,7 @@
       </c>
       <c r="C1" s="4" t="inlineStr">
         <is>
-          <t>多条规则同时命中时, 每个输出列取优先级数字最小的那条; 输出格填 - 表示不改; 同一行各条件之间是 AND, 不同行之间是 OR</t>
+          <t>多条规则同时命中时, 每个输出列取优先级数字最小的那条; 输出格填 - 表示不改; 同一行各条件之间是 AND, 相邻同 ID 行是同一规则的 OR 分支</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1277,7 @@
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>R5a</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="B8" s="10" t="n">
@@ -1332,19 +1345,17 @@
       </c>
       <c r="O8" s="13" t="inlineStr">
         <is>
-          <t>本月电话为空, 提醒补录。R5a + R5b 两行 = YAML 里 R5 的「任一满足」(决策表没有 OR, 用多行表达)</t>
+          <t>本月电话为空, 提醒补录。下一行同 ID = 同一条规则的另一个「或」分支 (YAML 里 R5 的 任一满足)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>R5b</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="n">
-        <v>5</v>
-      </c>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="n"/>
       <c r="C9" s="11" t="inlineStr">
         <is>
           <t>-</t>
@@ -1400,14 +1411,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N9" s="12" t="inlineStr">
-        <is>
-          <t>电话有缺失</t>
-        </is>
-      </c>
+      <c r="N9" s="12" t="n"/>
       <c r="O9" s="13" t="inlineStr">
         <is>
-          <t>主表电话为空, 提醒补录</t>
+          <t>主表电话为空, 提醒补录。续行的优先级和输出留空 (或与首行相同)</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1905,7 @@
       </c>
       <c r="N9" s="13" t="inlineStr">
         <is>
-          <t>金卡 4% 落在 R4 区间; 本月电话空不触发 R3 但触发 R5a</t>
+          <t>金卡 4% 落在 R4 区间; 本月电话空不触发 R3 但触发 R5</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2013,7 @@
       </c>
       <c r="N11" s="13" t="inlineStr">
         <is>
-          <t>主表电话空, 触发 R5b</t>
+          <t>主表电话空, 触发 R5 的第二个分支</t>
         </is>
       </c>
     </row>

--- a/examples/customer-sync/规则_决策表.xlsx
+++ b/examples/customer-sync/规则_决策表.xlsx
@@ -669,7 +669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -762,11 +762,24 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>可用函数</t>
+          <t>空值</t>
         </is>
       </c>
       <c r="B7" s="3" t="n"/>
       <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>x == 空 / x != 空 判空 (也认 为空(x) / 非空(x)); 空 只能和 == / != 搭配</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>可用函数</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n"/>
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>abs  round  天数差(晚, 早)  非空(x)  为空(x)  属于(x, 值1, 值2, ...)</t>
         </is>

--- a/examples/customer-sync/规则_决策表.xlsx
+++ b/examples/customer-sync/规则_决策表.xlsx
@@ -7,10 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="匹配设置" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="变量定义" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="决策表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="测试" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="输入" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="设置" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="变量定义" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="决策表" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="测试" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -499,26 +500,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="80" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>设置项</t>
+          <t>名称</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>值</t>
+          <t>匹配</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>重复键</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>文件</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
@@ -527,134 +540,50 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>左表</t>
+          <t>客户</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
+          <t>主表</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
           <t>客户主表.xlsx</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>被更新的表, 相对路径以本规则文件所在目录为基准</t>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>被更新的表: 输出的行就是它的行。规则里引用它的列写 客户.状态; 相对路径以本规则文件所在目录为基准</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>右表</t>
+          <t>本月</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
+          <t>客户编号</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>取第一条</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>本月流水.xlsx</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>参照表, 只读</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>左表别名</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>主表</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>规则里引用左表字段的前缀, 如 主表.状态</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>右表别名</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>本月</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>规则里引用右表字段的前缀, 如 本月.金额</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>匹配键</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>客户编号</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>两表按此列对行, 多列用逗号分隔</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>右表重复键</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>取第一条</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>一对多时的处理: 取第一条 / 报错</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>基准日期</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n">
-        <v>46314</v>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>天数差计算用的「今天」, 固定下来保证每次运行结果一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>输出</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>output/客户主表_更新后.xlsx</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>结果文件, 原表不动</t>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>参照表, 按 客户编号 对齐到主表 (多个键用逗号分隔); 引用写 本月.金额, 本月.存在 = 是否匹配到</t>
         </is>
       </c>
     </row>
@@ -664,6 +593,74 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>设置项</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>基准日期</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n">
+        <v>46314</v>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>天数差计算用的「今天」, 固定下来保证每次运行结果一致; 不写取运行当天</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>输出</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>output/客户主表_更新后.xlsx</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>默认输出路径, 命令行 -o 可覆盖; 不写则是 output/&lt;主表文件名&gt;_更新后.xlsx</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -702,7 +699,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>abs(本月.金额 - 主表.金额) / 主表.金额</t>
+          <t>abs(本月.金额 - 客户.金额) / 客户.金额</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -719,12 +716,12 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>天数差(基准日期, 主表.上次活跃)</t>
+          <t>天数差(基准日期, 客户.上次活跃)</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>基准日期见「匹配设置」</t>
+          <t>基准日期见「设置」</t>
         </is>
       </c>
     </row>
@@ -742,7 +739,7 @@
       <c r="B5" s="3" t="n"/>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>主表.&lt;列名&gt;  本月.&lt;列名&gt;  本月.存在(右表是否匹配到)  基准日期</t>
+          <t>客户.&lt;列名&gt;  本月.&lt;列名&gt;  本月.存在(参照表是否匹配到)  基准日期</t>
         </is>
       </c>
     </row>
@@ -790,7 +787,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -923,12 +920,12 @@
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>主表.状态</t>
+          <t>客户.状态</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>主表.等级</t>
+          <t>客户.等级</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr">
@@ -953,7 +950,7 @@
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
-          <t>主表.电话</t>
+          <t>客户.电话</t>
         </is>
       </c>
       <c r="J3" s="8" t="inlineStr">
@@ -1173,7 +1170,7 @@
       </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
-          <t>!= 主表.电话</t>
+          <t>!= 客户.电话</t>
         </is>
       </c>
       <c r="I6" s="11" t="inlineStr">
@@ -1436,7 +1433,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1554,12 +1551,12 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>主表.状态</t>
+          <t>客户.状态</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>主表.等级</t>
+          <t>客户.等级</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
@@ -1579,7 +1576,7 @@
       </c>
       <c r="G3" s="7" t="inlineStr">
         <is>
-          <t>主表.电话</t>
+          <t>客户.电话</t>
         </is>
       </c>
       <c r="H3" s="7" t="inlineStr">

--- a/examples/customer-sync/规则_决策表.xlsx
+++ b/examples/customer-sync/规则_决策表.xlsx
@@ -778,7 +778,7 @@
       <c r="B8" s="3" t="n"/>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>abs  round  天数差(晚, 早)  非空(x)  为空(x)  属于(x, 值1, 值2, ...)</t>
+          <t>abs  round  天数差(晚, 早)  非空(x)  为空(x)  属于(x, 值1, ...)  包含 / 不包含 / 开头是 / 开头不是 / 结尾是 / 结尾不是 (x, 文本1, ...)  拼接(a, b, ...)  数字(x)  如果(条件, 真值, 假值)</t>
         </is>
       </c>
     </row>

--- a/examples/customer-sync/规则_决策表.xlsx
+++ b/examples/customer-sync/规则_决策表.xlsx
@@ -23,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,6 +34,7 @@
     <font>
       <b val="1"/>
     </font>
+    <font/>
   </fonts>
   <fills count="7">
     <fill>
@@ -97,42 +98,42 @@
   <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -504,10 +505,10 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="80" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -537,7 +538,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>客户</t>
@@ -560,7 +561,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="32" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>本月</t>
@@ -601,9 +602,9 @@
   <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -632,13 +633,13 @@
       <c r="B2" s="5" t="n">
         <v>46314</v>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>天数差计算用的「今天」, 固定下来保证每次运行结果一致; 不写取运行当天</t>
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="32" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>输出</t>
@@ -670,8 +671,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -702,7 +703,7 @@
           <t>abs(本月.金额 - 客户.金额) / 客户.金额</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>本月金额相对主表金额的偏差比例, 本月缺失时为空</t>
         </is>
@@ -719,7 +720,7 @@
           <t>天数差(基准日期, 客户.上次活跃)</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>基准日期见「设置」</t>
         </is>
@@ -728,7 +729,7 @@
     <row r="4">
       <c r="A4" s="2" t="n"/>
       <c r="B4" s="3" t="n"/>
-      <c r="C4" s="4" t="n"/>
+      <c r="C4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -737,7 +738,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n"/>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>客户.&lt;列名&gt;  本月.&lt;列名&gt;  本月.存在(参照表是否匹配到)  基准日期</t>
         </is>
@@ -750,13 +751,13 @@
         </is>
       </c>
       <c r="B6" s="3" t="n"/>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>且 / 或 / 非 (也认 and / or / not), 两侧留空格; 可用括号分组</t>
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="32" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>空值</t>
@@ -769,7 +770,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="47" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>可用函数</t>
@@ -798,19 +799,19 @@
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="44" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -819,610 +820,610 @@
           <t>命中策略</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>优先级</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>多条规则同时命中时, 每个输出列取优先级数字最小的那条; 输出格填 - 表示不改; 同一行各条件之间是 AND, 相邻同 ID 行是同一规则的 OR 分支</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>规则ID</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>优先级</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="E2" s="8" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="F2" s="8" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="G2" s="8" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="H2" s="7" t="inlineStr">
+      <c r="H2" s="8" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="I2" s="7" t="inlineStr">
+      <c r="I2" s="8" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="J2" s="8" t="inlineStr">
+      <c r="J2" s="9" t="inlineStr">
         <is>
           <t>输出</t>
         </is>
       </c>
-      <c r="K2" s="8" t="inlineStr">
+      <c r="K2" s="9" t="inlineStr">
         <is>
           <t>输出</t>
         </is>
       </c>
-      <c r="L2" s="8" t="inlineStr">
+      <c r="L2" s="9" t="inlineStr">
         <is>
           <t>输出</t>
         </is>
       </c>
-      <c r="M2" s="8" t="inlineStr">
+      <c r="M2" s="9" t="inlineStr">
         <is>
           <t>输出</t>
         </is>
       </c>
-      <c r="N2" s="8" t="inlineStr">
+      <c r="N2" s="9" t="inlineStr">
         <is>
           <t>输出</t>
         </is>
       </c>
-      <c r="O2" s="9" t="inlineStr">
+      <c r="O2" s="10" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>规则ID</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>优先级</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>客户.状态</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>客户.等级</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>偏差率</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F3" s="8" t="inlineStr">
         <is>
           <t>本月.存在</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="G3" s="8" t="inlineStr">
         <is>
           <t>距上次活跃天数</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
+      <c r="H3" s="8" t="inlineStr">
         <is>
           <t>本月.电话</t>
         </is>
       </c>
-      <c r="I3" s="7" t="inlineStr">
+      <c r="I3" s="8" t="inlineStr">
         <is>
           <t>客户.电话</t>
         </is>
       </c>
-      <c r="J3" s="8" t="inlineStr">
+      <c r="J3" s="9" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="K3" s="9" t="inlineStr">
         <is>
           <t>电话</t>
         </is>
       </c>
-      <c r="L3" s="8" t="inlineStr">
+      <c r="L3" s="9" t="inlineStr">
         <is>
           <t>复核标记</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr">
+      <c r="M3" s="9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
-      <c r="N3" s="8" t="inlineStr">
+      <c r="N3" s="9" t="inlineStr">
         <is>
           <t>提醒</t>
         </is>
       </c>
-      <c r="O3" s="9" t="inlineStr">
+      <c r="O3" s="10" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="B4" s="10" t="n">
+      <c r="B4" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>活跃</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
         <is>
           <t>&gt; 0.05</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H4" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I4" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J4" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K4" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" s="12" t="inlineStr">
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H4" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I4" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J4" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L4" s="13" t="inlineStr">
         <is>
           <t>待复核</t>
         </is>
       </c>
-      <c r="M4" s="12" t="inlineStr">
+      <c r="M4" s="13" t="inlineStr">
         <is>
           <t>金额偏差超 5%</t>
         </is>
       </c>
-      <c r="N4" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O4" s="13" t="inlineStr">
+      <c r="N4" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O4" s="6" t="inlineStr">
         <is>
           <t>活跃客户金额偏差超 5% 需复核</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="B5" s="10" t="n">
+      <c r="B5" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>!= 休眠</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G5" s="11" t="inlineStr">
+      <c r="G5" s="12" t="inlineStr">
         <is>
           <t>&gt; 180</t>
         </is>
       </c>
-      <c r="H5" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I5" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J5" s="12" t="inlineStr">
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J5" s="13" t="inlineStr">
         <is>
           <t>休眠</t>
         </is>
       </c>
-      <c r="K5" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L5" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M5" s="12" t="inlineStr">
+      <c r="K5" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L5" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M5" s="13" t="inlineStr">
         <is>
           <t>连续 6 个月无流水</t>
         </is>
       </c>
-      <c r="N5" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O5" s="13" t="inlineStr">
+      <c r="N5" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O5" s="6" t="inlineStr">
         <is>
           <t>本月无流水且长期不活跃, 转休眠</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
       </c>
-      <c r="B6" s="10" t="n">
+      <c r="B6" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D6" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E6" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H6" s="11" t="inlineStr">
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
         <is>
           <t>!= 客户.电话</t>
         </is>
       </c>
-      <c r="I6" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J6" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K6" s="12" t="inlineStr">
+      <c r="I6" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J6" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="13" t="inlineStr">
         <is>
           <t>本月.电话</t>
         </is>
       </c>
-      <c r="L6" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M6" s="12" t="inlineStr">
+      <c r="L6" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M6" s="13" t="inlineStr">
         <is>
           <t>电话变更</t>
         </is>
       </c>
-      <c r="N6" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O6" s="13" t="inlineStr">
+      <c r="N6" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O6" s="6" t="inlineStr">
         <is>
           <t>本月电话与主表不同则覆盖 (本月电话为空不算不同)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>R4</t>
         </is>
       </c>
-      <c r="B7" s="10" t="n">
+      <c r="B7" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>活跃</t>
         </is>
       </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>VIP, 金卡</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>[0.02..0.05]</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr">
+      <c r="F7" s="12" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G7" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H7" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I7" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J7" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K7" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L7" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M7" s="12" t="inlineStr">
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H7" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I7" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J7" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L7" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M7" s="13" t="inlineStr">
         <is>
           <t>VIP 小幅偏差, 关注</t>
         </is>
       </c>
-      <c r="N7" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O7" s="13" t="inlineStr">
+      <c r="N7" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O7" s="6" t="inlineStr">
         <is>
           <t>高等级客户小幅偏差也要留意</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>R5</t>
         </is>
       </c>
-      <c r="B8" s="10" t="n">
+      <c r="B8" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E8" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="11" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G8" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H8" s="11" t="inlineStr">
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H8" s="12" t="inlineStr">
         <is>
           <t>为空</t>
         </is>
       </c>
-      <c r="I8" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J8" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K8" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L8" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M8" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N8" s="12" t="inlineStr">
+      <c r="I8" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J8" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L8" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M8" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="13" t="inlineStr">
         <is>
           <t>电话有缺失</t>
         </is>
       </c>
-      <c r="O8" s="13" t="inlineStr">
+      <c r="O8" s="4" t="inlineStr">
         <is>
           <t>本月电话为空, 提醒补录。下一行同 ID = 同一条规则的另一个「或」分支 (YAML 里 R5 的 任一满足)</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>R5</t>
         </is>
       </c>
-      <c r="B9" s="10" t="n"/>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E9" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="11" t="inlineStr">
+      <c r="B9" s="11" t="n"/>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G9" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H9" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I9" s="11" t="inlineStr">
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H9" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I9" s="12" t="inlineStr">
         <is>
           <t>为空</t>
         </is>
       </c>
-      <c r="J9" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K9" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L9" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M9" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N9" s="12" t="n"/>
-      <c r="O9" s="13" t="inlineStr">
+      <c r="J9" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L9" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M9" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="13" t="n"/>
+      <c r="O9" s="4" t="inlineStr">
         <is>
           <t>主表电话为空, 提醒补录。续行的优先级和输出留空 (或与首行相同)</t>
         </is>
@@ -1442,20 +1443,20 @@
   <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="40" customWidth="1" min="14" max="14"/>
+    <col width="53" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1464,564 +1465,563 @@
           <t>说明</t>
         </is>
       </c>
-      <c r="B1" s="3" t="n"/>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>每行一个用例: 填输入变量的值, 期望列留空表示「该列不变」。运行时先跑本表, 全部通过才处理真实数据</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>用例</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="E2" s="8" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="F2" s="8" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="G2" s="8" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="H2" s="7" t="inlineStr">
+      <c r="H2" s="8" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="I2" s="8" t="inlineStr">
+      <c r="I2" s="9" t="inlineStr">
         <is>
           <t>期望</t>
         </is>
       </c>
-      <c r="J2" s="8" t="inlineStr">
+      <c r="J2" s="9" t="inlineStr">
         <is>
           <t>期望</t>
         </is>
       </c>
-      <c r="K2" s="8" t="inlineStr">
+      <c r="K2" s="9" t="inlineStr">
         <is>
           <t>期望</t>
         </is>
       </c>
-      <c r="L2" s="8" t="inlineStr">
+      <c r="L2" s="9" t="inlineStr">
         <is>
           <t>期望</t>
         </is>
       </c>
-      <c r="M2" s="8" t="inlineStr">
+      <c r="M2" s="9" t="inlineStr">
         <is>
           <t>期望</t>
         </is>
       </c>
-      <c r="N2" s="9" t="inlineStr">
+      <c r="N2" s="10" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>用例</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>客户.状态</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>客户.等级</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>偏差率</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>本月.存在</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F3" s="8" t="inlineStr">
         <is>
           <t>距上次活跃天数</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="G3" s="8" t="inlineStr">
         <is>
           <t>客户.电话</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
+      <c r="H3" s="8" t="inlineStr">
         <is>
           <t>本月.电话</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" s="9" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="J3" s="8" t="inlineStr">
+      <c r="J3" s="9" t="inlineStr">
         <is>
           <t>电话</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="K3" s="9" t="inlineStr">
         <is>
           <t>复核标记</t>
         </is>
       </c>
-      <c r="L3" s="8" t="inlineStr">
+      <c r="L3" s="9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr">
+      <c r="M3" s="9" t="inlineStr">
         <is>
           <t>提醒</t>
         </is>
       </c>
-      <c r="N3" s="9" t="inlineStr">
+      <c r="N3" s="10" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>活跃</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="D4" s="11" t="n">
+      <c r="D4" s="12" t="n">
         <v>0.08</v>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="12" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="F4" s="11" t="n">
+      <c r="F4" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="12" t="inlineStr">
         <is>
           <t>13800000001</t>
         </is>
       </c>
-      <c r="H4" s="11" t="inlineStr">
+      <c r="H4" s="12" t="inlineStr">
         <is>
           <t>13800000001</t>
         </is>
       </c>
-      <c r="I4" s="12" t="n"/>
-      <c r="J4" s="12" t="n"/>
-      <c r="K4" s="12" t="inlineStr">
+      <c r="I4" s="13" t="n"/>
+      <c r="J4" s="13" t="n"/>
+      <c r="K4" s="13" t="inlineStr">
         <is>
           <t>待复核</t>
         </is>
       </c>
-      <c r="L4" s="12" t="inlineStr">
+      <c r="L4" s="13" t="inlineStr">
         <is>
           <t>金额偏差超 5%</t>
         </is>
       </c>
-      <c r="M4" s="12" t="n"/>
-      <c r="N4" s="13" t="inlineStr">
+      <c r="M4" s="13" t="n"/>
+      <c r="N4" s="6" t="inlineStr">
         <is>
           <t>偏差 8% 触发 R1</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>活跃</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="D5" s="11" t="n">
+      <c r="D5" s="12" t="n">
         <v>0.03</v>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="F5" s="11" t="n">
+      <c r="F5" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="G5" s="11" t="inlineStr">
+      <c r="G5" s="12" t="inlineStr">
         <is>
           <t>13800000002</t>
         </is>
       </c>
-      <c r="H5" s="11" t="inlineStr">
+      <c r="H5" s="12" t="inlineStr">
         <is>
           <t>13800000002</t>
         </is>
       </c>
-      <c r="I5" s="12" t="n"/>
-      <c r="J5" s="12" t="n"/>
-      <c r="K5" s="12" t="n"/>
-      <c r="L5" s="12" t="n"/>
-      <c r="M5" s="12" t="n"/>
-      <c r="N5" s="13" t="inlineStr">
+      <c r="I5" s="13" t="n"/>
+      <c r="J5" s="13" t="n"/>
+      <c r="K5" s="13" t="n"/>
+      <c r="L5" s="13" t="n"/>
+      <c r="M5" s="13" t="n"/>
+      <c r="N5" s="6" t="inlineStr">
         <is>
           <t>偏差 3% 普通客户, 什么都不发生</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>活跃</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="D6" s="11" t="n"/>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="D6" s="12" t="n"/>
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="F6" s="11" t="n">
+      <c r="F6" s="12" t="n">
         <v>200</v>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="12" t="inlineStr">
         <is>
           <t>13800000003</t>
         </is>
       </c>
-      <c r="H6" s="11" t="n"/>
-      <c r="I6" s="12" t="inlineStr">
+      <c r="H6" s="12" t="n"/>
+      <c r="I6" s="13" t="inlineStr">
         <is>
           <t>休眠</t>
         </is>
       </c>
-      <c r="J6" s="12" t="n"/>
-      <c r="K6" s="12" t="n"/>
-      <c r="L6" s="12" t="inlineStr">
+      <c r="J6" s="13" t="n"/>
+      <c r="K6" s="13" t="n"/>
+      <c r="L6" s="13" t="inlineStr">
         <is>
           <t>连续 6 个月无流水</t>
         </is>
       </c>
-      <c r="M6" s="12" t="n"/>
-      <c r="N6" s="13" t="inlineStr">
+      <c r="M6" s="13" t="n"/>
+      <c r="N6" s="6" t="inlineStr">
         <is>
           <t>本月缺失且 200 天, 触发 R2</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>休眠</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="D7" s="11" t="n"/>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="D7" s="12" t="n"/>
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="F7" s="11" t="n">
+      <c r="F7" s="12" t="n">
         <v>400</v>
       </c>
-      <c r="G7" s="11" t="inlineStr">
+      <c r="G7" s="12" t="inlineStr">
         <is>
           <t>13800000007</t>
         </is>
       </c>
-      <c r="H7" s="11" t="n"/>
-      <c r="I7" s="12" t="n"/>
-      <c r="J7" s="12" t="n"/>
-      <c r="K7" s="12" t="n"/>
-      <c r="L7" s="12" t="n"/>
-      <c r="M7" s="12" t="n"/>
-      <c r="N7" s="13" t="inlineStr">
+      <c r="H7" s="12" t="n"/>
+      <c r="I7" s="13" t="n"/>
+      <c r="J7" s="13" t="n"/>
+      <c r="K7" s="13" t="n"/>
+      <c r="L7" s="13" t="n"/>
+      <c r="M7" s="13" t="n"/>
+      <c r="N7" s="6" t="inlineStr">
         <is>
           <t>已休眠不重复命中 R2</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>T5</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>试用</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="D8" s="11" t="n">
+      <c r="D8" s="12" t="n">
         <v>0.3</v>
       </c>
-      <c r="E8" s="11" t="inlineStr">
+      <c r="E8" s="12" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="F8" s="11" t="n">
+      <c r="F8" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G8" s="11" t="inlineStr">
+      <c r="G8" s="12" t="inlineStr">
         <is>
           <t>13800000005</t>
         </is>
       </c>
-      <c r="H8" s="11" t="inlineStr">
+      <c r="H8" s="12" t="inlineStr">
         <is>
           <t>13900000005</t>
         </is>
       </c>
-      <c r="I8" s="12" t="n"/>
-      <c r="J8" s="12" t="inlineStr">
+      <c r="I8" s="13" t="n"/>
+      <c r="J8" s="13" t="inlineStr">
         <is>
           <t>13900000005</t>
         </is>
       </c>
-      <c r="K8" s="12" t="n"/>
-      <c r="L8" s="12" t="inlineStr">
+      <c r="K8" s="13" t="n"/>
+      <c r="L8" s="13" t="inlineStr">
         <is>
           <t>电话变更</t>
         </is>
       </c>
-      <c r="M8" s="12" t="n"/>
-      <c r="N8" s="13" t="inlineStr">
+      <c r="M8" s="13" t="n"/>
+      <c r="N8" s="6" t="inlineStr">
         <is>
           <t>试用客户不触发 R1, 只换电话</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>T6</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>活跃</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>金卡</t>
         </is>
       </c>
-      <c r="D9" s="11" t="n">
+      <c r="D9" s="12" t="n">
         <v>0.04</v>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="F9" s="11" t="n">
+      <c r="F9" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="G9" s="11" t="inlineStr">
+      <c r="G9" s="12" t="inlineStr">
         <is>
           <t>13800000008</t>
         </is>
       </c>
-      <c r="H9" s="11" t="n"/>
-      <c r="I9" s="12" t="n"/>
-      <c r="J9" s="12" t="n"/>
-      <c r="K9" s="12" t="n"/>
-      <c r="L9" s="12" t="inlineStr">
+      <c r="H9" s="12" t="n"/>
+      <c r="I9" s="13" t="n"/>
+      <c r="J9" s="13" t="n"/>
+      <c r="K9" s="13" t="n"/>
+      <c r="L9" s="13" t="inlineStr">
         <is>
           <t>VIP 小幅偏差, 关注</t>
         </is>
       </c>
-      <c r="M9" s="12" t="inlineStr">
+      <c r="M9" s="13" t="inlineStr">
         <is>
           <t>电话有缺失</t>
         </is>
       </c>
-      <c r="N9" s="13" t="inlineStr">
+      <c r="N9" s="6" t="inlineStr">
         <is>
           <t>金卡 4% 落在 R4 区间; 本月电话空不触发 R3 但触发 R5</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>T7</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>活跃</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>VIP</t>
         </is>
       </c>
-      <c r="D10" s="11" t="n">
+      <c r="D10" s="12" t="n">
         <v>0.08</v>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="E10" s="12" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="F10" s="11" t="n">
+      <c r="F10" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="G10" s="12" t="inlineStr">
         <is>
           <t>13800000006</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="H10" s="12" t="inlineStr">
         <is>
           <t>13900000006</t>
         </is>
       </c>
-      <c r="I10" s="12" t="n"/>
-      <c r="J10" s="12" t="inlineStr">
+      <c r="I10" s="13" t="n"/>
+      <c r="J10" s="13" t="inlineStr">
         <is>
           <t>13900000006</t>
         </is>
       </c>
-      <c r="K10" s="12" t="inlineStr">
+      <c r="K10" s="13" t="inlineStr">
         <is>
           <t>待复核</t>
         </is>
       </c>
-      <c r="L10" s="12" t="inlineStr">
+      <c r="L10" s="13" t="inlineStr">
         <is>
           <t>金额偏差超 5%</t>
         </is>
       </c>
-      <c r="M10" s="12" t="n"/>
-      <c r="N10" s="13" t="inlineStr">
+      <c r="M10" s="13" t="n"/>
+      <c r="N10" s="6" t="inlineStr">
         <is>
           <t>R1 与 R3 同时命中, 备注听优先级高的 R1</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>T8</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>活跃</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="D11" s="11" t="n">
+      <c r="D11" s="12" t="n">
         <v>0.01</v>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="F11" s="11" t="n">
+      <c r="F11" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G11" s="11" t="n"/>
-      <c r="H11" s="11" t="inlineStr">
+      <c r="G11" s="12" t="n"/>
+      <c r="H11" s="12" t="inlineStr">
         <is>
           <t>13800000009</t>
         </is>
       </c>
-      <c r="I11" s="12" t="n"/>
-      <c r="J11" s="12" t="n"/>
-      <c r="K11" s="12" t="n"/>
-      <c r="L11" s="12" t="n"/>
-      <c r="M11" s="12" t="inlineStr">
+      <c r="I11" s="13" t="n"/>
+      <c r="J11" s="13" t="n"/>
+      <c r="K11" s="13" t="n"/>
+      <c r="L11" s="13" t="n"/>
+      <c r="M11" s="13" t="inlineStr">
         <is>
           <t>电话有缺失</t>
         </is>
       </c>
-      <c r="N11" s="13" t="inlineStr">
+      <c r="N11" s="6" t="inlineStr">
         <is>
           <t>主表电话空, 触发 R5 的第二个分支</t>
         </is>

--- a/examples/customer-sync/规则_决策表.xlsx
+++ b/examples/customer-sync/规则_决策表.xlsx
@@ -599,7 +599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -624,7 +624,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>基准日期</t>
@@ -633,9 +633,9 @@
       <c r="B2" s="5" t="n">
         <v>46314</v>
       </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>天数差计算用的「今天」, 固定下来保证每次运行结果一致; 不写取运行当天</t>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>天数差 / N天 等日期计算用的「今天」, 日期格或 2026-10-19 文本都行。留空取运行当天; 固定下来保证每次结果一致</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,38 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>默认输出路径, 命令行 -o 可覆盖; 不写则是 output/&lt;主表文件名&gt;_更新后.xlsx</t>
+          <t>默认输出路径, 相对本规则文件所在目录, 命令行 -o 可覆盖。留空为 output/&lt;主表文件名&gt;_更新后.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>拼接分隔符</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>命中策略 多条拼接 用的分隔符, 留空为 /。本表策略是 优先级, 填了会报错</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n"/>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="6" t="n"/>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>可用设置项</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>只认上面三个, 写别的加载时报错 (不会静默忽略); 只读 A 列 (设置项) 和 B 列 (值), B 列留空 = 取默认值; 本列是说明, 不参与解析</t>
         </is>
       </c>
     </row>

--- a/examples/customer-sync/规则_决策表.xlsx
+++ b/examples/customer-sync/规则_决策表.xlsx
@@ -7,11 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="输入" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="设置" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="变量定义" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="决策表" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="测试" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="设置" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="变量定义" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="决策表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="测试" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -45,12 +44,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
     <fill>
@@ -97,23 +96,23 @@
   </cellStyleXfs>
   <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -124,7 +123,7 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -501,11 +500,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="70" customWidth="1" min="5" max="5"/>
@@ -514,75 +513,120 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>基准日期</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n">
+        <v>46314</v>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>天数差 / N天 等日期计算用的「今天」, 日期格或 2026-10-19 文本都行。留空取运行当天; 每批不同的在运行时给 (--var 基准日期=...), 这里的值仍是内嵌测试用的</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>输出</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>output/客户主表_更新后.xlsx</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>默认输出路径, 相对本规则文件所在目录, 命令行 -o 可覆盖。留空为 output/&lt;主表文件名&gt;_更新后.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>可用设置项</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>只认 基准日期 / 输出, 写别的加载时报错 (不会静默忽略); B 列留空 = 取默认值。下面「名称 / 匹配」那一行起是输入表</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>匹配</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>重复键</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>文件</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>客户</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>主表</t>
         </is>
       </c>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>客户主表.xlsx</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>被更新的表: 输出的行就是它的行。规则里引用它的列写 客户.状态; 相对路径以本规则文件所在目录为基准</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>本月</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>客户编号</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>取第一条</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>本月流水.xlsx</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>参照表, 按 客户编号 对齐到主表 (多个键用逗号分隔); 引用写 本月.金额, 本月.存在 = 是否匹配到</t>
         </is>
@@ -594,105 +638,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>设置项</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>值</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>基准日期</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="n">
-        <v>46314</v>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>天数差 / N天 等日期计算用的「今天」, 日期格或 2026-10-19 文本都行。留空取运行当天; 固定下来保证每次结果一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>输出</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>output/客户主表_更新后.xlsx</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>默认输出路径, 相对本规则文件所在目录, 命令行 -o 可覆盖。留空为 output/&lt;主表文件名&gt;_更新后.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>拼接分隔符</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>命中策略 多条拼接 用的分隔符, 留空为 /。本表策略是 优先级, 填了会报错</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n"/>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="6" t="n"/>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>可用设置项</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>只认上面三个, 写别的加载时报错 (不会静默忽略); 只读 A 列 (设置项) 和 B 列 (值), B 列留空 = 取默认值; 本列是说明, 不参与解析</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -707,108 +652,108 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>变量</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>定义</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>偏差率</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>abs(本月.金额 - 客户.金额) / 客户.金额</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>本月金额相对主表金额的偏差比例, 本月缺失时为空</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>距上次活跃天数</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>天数差(基准日期, 客户.上次活跃)</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>基准日期见「设置」</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n"/>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="6" t="n"/>
+      <c r="A4" s="1" t="n"/>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="3" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>内置变量</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>客户.&lt;列名&gt;  本月.&lt;列名&gt;  本月.存在(参照表是否匹配到)  基准日期</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>连接词</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>且 / 或 / 非 (也认 and / or / not), 两侧留空格; 可用括号分组</t>
         </is>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>空值</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n"/>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>x == 空 / x != 空 判空 (也认 为空(x) / 非空(x)); 空 只能和 == / != 搭配</t>
         </is>
       </c>
     </row>
     <row r="8" ht="47" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>可用函数</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n"/>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>abs  round  天数差(晚, 早)  非空(x)  为空(x)  属于(x, 值1, ...)  包含 / 不包含 / 开头是 / 开头不是 / 结尾是 / 结尾不是 (x, 文本1, ...)  拼接(a, b, ...)  数字(x)  如果(条件, 真值, 假值)</t>
         </is>
@@ -819,7 +764,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -846,17 +791,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>命中策略</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>优先级</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>多条规则同时命中时, 每个输出列取优先级数字最小的那条; 输出格填 - 表示不改; 同一行各条件之间是 AND, 相邻同 ID 行是同一规则的 OR 分支</t>
         </is>
@@ -1085,7 +1030,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O4" s="6" t="inlineStr">
+      <c r="O4" s="3" t="inlineStr">
         <is>
           <t>活跃客户金额偏差超 5% 需复核</t>
         </is>
@@ -1160,7 +1105,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O5" s="6" t="inlineStr">
+      <c r="O5" s="3" t="inlineStr">
         <is>
           <t>本月无流水且长期不活跃, 转休眠</t>
         </is>
@@ -1235,7 +1180,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O6" s="6" t="inlineStr">
+      <c r="O6" s="3" t="inlineStr">
         <is>
           <t>本月电话与主表不同则覆盖 (本月电话为空不算不同)</t>
         </is>
@@ -1310,7 +1255,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O7" s="6" t="inlineStr">
+      <c r="O7" s="3" t="inlineStr">
         <is>
           <t>高等级客户小幅偏差也要留意</t>
         </is>
@@ -1385,7 +1330,7 @@
           <t>电话有缺失</t>
         </is>
       </c>
-      <c r="O8" s="4" t="inlineStr">
+      <c r="O8" s="6" t="inlineStr">
         <is>
           <t>本月电话为空, 提醒补录。下一行同 ID = 同一条规则的另一个「或」分支 (YAML 里 R5 的 任一满足)</t>
         </is>
@@ -1454,7 +1399,7 @@
         </is>
       </c>
       <c r="N9" s="13" t="n"/>
-      <c r="O9" s="4" t="inlineStr">
+      <c r="O9" s="6" t="inlineStr">
         <is>
           <t>主表电话为空, 提醒补录。续行的优先级和输出留空 (或与首行相同)</t>
         </is>
@@ -1465,7 +1410,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1491,12 +1436,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>每行一个用例: 填输入变量的值, 期望列留空表示「该列不变」。运行时先跑本表, 全部通过才处理真实数据</t>
         </is>
@@ -1696,7 +1641,7 @@
         </is>
       </c>
       <c r="M4" s="13" t="n"/>
-      <c r="N4" s="6" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>偏差 8% 触发 R1</t>
         </is>
@@ -1744,7 +1689,7 @@
       <c r="K5" s="13" t="n"/>
       <c r="L5" s="13" t="n"/>
       <c r="M5" s="13" t="n"/>
-      <c r="N5" s="6" t="inlineStr">
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>偏差 3% 普通客户, 什么都不发生</t>
         </is>
@@ -1794,7 +1739,7 @@
         </is>
       </c>
       <c r="M6" s="13" t="n"/>
-      <c r="N6" s="6" t="inlineStr">
+      <c r="N6" s="3" t="inlineStr">
         <is>
           <t>本月缺失且 200 天, 触发 R2</t>
         </is>
@@ -1836,7 +1781,7 @@
       <c r="K7" s="13" t="n"/>
       <c r="L7" s="13" t="n"/>
       <c r="M7" s="13" t="n"/>
-      <c r="N7" s="6" t="inlineStr">
+      <c r="N7" s="3" t="inlineStr">
         <is>
           <t>已休眠不重复命中 R2</t>
         </is>
@@ -1892,7 +1837,7 @@
         </is>
       </c>
       <c r="M8" s="13" t="n"/>
-      <c r="N8" s="6" t="inlineStr">
+      <c r="N8" s="3" t="inlineStr">
         <is>
           <t>试用客户不触发 R1, 只换电话</t>
         </is>
@@ -1944,7 +1889,7 @@
           <t>电话有缺失</t>
         </is>
       </c>
-      <c r="N9" s="6" t="inlineStr">
+      <c r="N9" s="3" t="inlineStr">
         <is>
           <t>金卡 4% 落在 R4 区间; 本月电话空不触发 R3 但触发 R5</t>
         </is>
@@ -2004,7 +1949,7 @@
         </is>
       </c>
       <c r="M10" s="13" t="n"/>
-      <c r="N10" s="6" t="inlineStr">
+      <c r="N10" s="3" t="inlineStr">
         <is>
           <t>R1 与 R3 同时命中, 备注听优先级高的 R1</t>
         </is>
@@ -2052,7 +1997,7 @@
           <t>电话有缺失</t>
         </is>
       </c>
-      <c r="N11" s="6" t="inlineStr">
+      <c r="N11" s="3" t="inlineStr">
         <is>
           <t>主表电话空, 触发 R5 的第二个分支</t>
         </is>

--- a/examples/customer-sync/规则_决策表.xlsx
+++ b/examples/customer-sync/规则_决策表.xlsx
@@ -99,10 +99,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -500,133 +500,145 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="30.4" customWidth="1" min="2" max="2"/>
+    <col width="10.8" customWidth="1" min="3" max="3"/>
+    <col width="15.8" customWidth="1" min="4" max="4"/>
     <col width="70" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>基准日期</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n">
-        <v>46314</v>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>天数差 / N天 等日期计算用的「今天」, 日期格或 2026-10-19 文本都行。留空取运行当天; 每批不同的在运行时给 (--var 基准日期=...), 这里的值仍是内嵌测试用的</t>
+          <t>设置项</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>每行一项: A 列名字 / B 列值 / 再往右是说明; 只认 基准日期 / 输出, 写别的加载时报错; B 列留空 = 取默认值</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>输出</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>output/客户主表_更新后.xlsx</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>默认输出路径, 相对本规则文件所在目录, 命令行 -o 可覆盖。留空为 output/&lt;主表文件名&gt;_更新后.xlsx</t>
+          <t>基准日期</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>46314</v>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>天数差 / N天 等日期计算用的「今天」, 日期格或 2026-10-19 文本都行。留空取运行当天; 每批不同的在运行时给 (--var 基准日期=...), 这里的值仍是内嵌测试用的</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>可用设置项</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>只认 基准日期 / 输出, 写别的加载时报错 (不会静默忽略); B 列留空 = 取默认值。下面「名称 / 匹配」那一行起是输入表</t>
+          <t>输出</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>output/客户主表_更新后.xlsx</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>默认输出路径, 相对本规则文件所在目录, 命令行 -o 可覆盖。留空为 output/&lt;主表文件名&gt;_更新后.xlsx</t>
         </is>
       </c>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>输入表</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>下一行是列名, 之后每行声明一个输入: 名称 = 规则里的前缀; 匹配 = 主表写 主表, 其它写对齐到主表的键; 文件 = 默认文件 (命令行 -i 可覆盖)。输入表下面不要再写别的</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>匹配</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>重复键</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>文件</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>客户</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>主表</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>客户主表.xlsx</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>被更新的表: 输出的行就是它的行。规则里引用它的列写 客户.状态; 相对路径以本规则文件所在目录为基准</t>
         </is>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
       <c r="A7" s="1" t="inlineStr">
         <is>
+          <t>客户</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>主表</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>客户主表.xlsx</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>被更新的表: 输出的行就是它的行。规则里引用它的列写 客户.状态; 相对路径以本规则文件所在目录为基准</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
           <t>本月</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>客户编号</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>取第一条</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>本月流水.xlsx</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>参照表, 按 客户编号 对齐到主表 (多个键用逗号分隔); 引用写 本月.金额, 本月.存在 = 是否匹配到</t>
         </is>
@@ -646,8 +658,8 @@
   <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="17.4" customWidth="1" min="1" max="1"/>
+    <col width="42.40000000000001" customWidth="1" min="2" max="2"/>
     <col width="70" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -679,7 +691,7 @@
           <t>abs(本月.金额 - 客户.金额) / 客户.金额</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>本月金额相对主表金额的偏差比例, 本月缺失时为空</t>
         </is>
@@ -696,7 +708,7 @@
           <t>天数差(基准日期, 客户.上次活跃)</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>基准日期见「设置」</t>
         </is>
@@ -705,7 +717,7 @@
     <row r="4">
       <c r="A4" s="1" t="n"/>
       <c r="B4" s="4" t="n"/>
-      <c r="C4" s="3" t="n"/>
+      <c r="C4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -714,7 +726,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n"/>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>客户.&lt;列名&gt;  本月.&lt;列名&gt;  本月.存在(参照表是否匹配到)  基准日期</t>
         </is>
@@ -727,7 +739,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n"/>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>且 / 或 / 非 (也认 and / or / not), 两侧留空格; 可用括号分组</t>
         </is>
@@ -773,20 +785,20 @@
   <dimension ref="A1:O9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="10.8" customWidth="1" min="1" max="1"/>
+    <col width="8.600000000000001" customWidth="1" min="2" max="2"/>
+    <col width="11.8" customWidth="1" min="3" max="3"/>
+    <col width="11.8" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11.8" customWidth="1" min="6" max="6"/>
+    <col width="17.4" customWidth="1" min="7" max="7"/>
+    <col width="14.8" customWidth="1" min="8" max="8"/>
+    <col width="11.8" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="11.8" customWidth="1" min="11" max="11"/>
+    <col width="10.8" customWidth="1" min="12" max="12"/>
+    <col width="21.2" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
@@ -796,12 +808,12 @@
           <t>命中策略</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>优先级</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>多条规则同时命中时, 每个输出列取优先级数字最小的那条; 输出格填 - 表示不改; 同一行各条件之间是 AND, 相邻同 ID 行是同一规则的 OR 分支</t>
         </is>
@@ -1030,7 +1042,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>活跃客户金额偏差超 5% 需复核</t>
         </is>
@@ -1105,7 +1117,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>本月无流水且长期不活跃, 转休眠</t>
         </is>
@@ -1180,7 +1192,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>本月电话与主表不同则覆盖 (本月电话为空不算不同)</t>
         </is>
@@ -1255,7 +1267,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>高等级客户小幅偏差也要留意</t>
         </is>
@@ -1420,19 +1432,19 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11.8" customWidth="1" min="2" max="2"/>
+    <col width="11.8" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="11.8" customWidth="1" min="5" max="5"/>
+    <col width="17.4" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="53" customWidth="1" min="14" max="14"/>
+    <col width="10.8" customWidth="1" min="11" max="11"/>
+    <col width="21.2" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="56.40000000000001" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1441,7 +1453,7 @@
           <t>说明</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>每行一个用例: 填输入变量的值, 期望列留空表示「该列不变」。运行时先跑本表, 全部通过才处理真实数据</t>
         </is>
@@ -1641,7 +1653,7 @@
         </is>
       </c>
       <c r="M4" s="13" t="n"/>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>偏差 8% 触发 R1</t>
         </is>
@@ -1689,7 +1701,7 @@
       <c r="K5" s="13" t="n"/>
       <c r="L5" s="13" t="n"/>
       <c r="M5" s="13" t="n"/>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>偏差 3% 普通客户, 什么都不发生</t>
         </is>
@@ -1739,7 +1751,7 @@
         </is>
       </c>
       <c r="M6" s="13" t="n"/>
-      <c r="N6" s="3" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>本月缺失且 200 天, 触发 R2</t>
         </is>
@@ -1781,7 +1793,7 @@
       <c r="K7" s="13" t="n"/>
       <c r="L7" s="13" t="n"/>
       <c r="M7" s="13" t="n"/>
-      <c r="N7" s="3" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>已休眠不重复命中 R2</t>
         </is>
@@ -1837,7 +1849,7 @@
         </is>
       </c>
       <c r="M8" s="13" t="n"/>
-      <c r="N8" s="3" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>试用客户不触发 R1, 只换电话</t>
         </is>
@@ -1889,7 +1901,7 @@
           <t>电话有缺失</t>
         </is>
       </c>
-      <c r="N9" s="3" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>金卡 4% 落在 R4 区间; 本月电话空不触发 R3 但触发 R5</t>
         </is>
@@ -1949,7 +1961,7 @@
         </is>
       </c>
       <c r="M10" s="13" t="n"/>
-      <c r="N10" s="3" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>R1 与 R3 同时命中, 备注听优先级高的 R1</t>
         </is>
@@ -1997,7 +2009,7 @@
           <t>电话有缺失</t>
         </is>
       </c>
-      <c r="N11" s="3" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>主表电话空, 触发 R5 的第二个分支</t>
         </is>

--- a/examples/customer-sync/规则_决策表.xlsx
+++ b/examples/customer-sync/规则_决策表.xlsx
@@ -22,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,15 +32,27 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font/>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -68,7 +80,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -90,49 +102,104 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -510,141 +577,157 @@
     <col width="70" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>设置项</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>每行一项: A 列名字 / B 列值 / 再往右是说明; 只认 基准日期 / 输出, 写别的加载时报错; B 列留空 = 取默认值</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="D1" s="4" t="n"/>
+      <c r="E1" s="5" t="n"/>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>基准日期</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" s="7" t="n">
         <v>46314</v>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>天数差 / N天 等日期计算用的「今天」, 日期格或 2026-10-19 文本都行。留空取运行当天; 每批不同的在运行时给 (--var 基准日期=...), 这里的值仍是内嵌测试用的</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="5" t="n"/>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>输出</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>output/客户主表_更新后.xlsx</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>默认输出路径, 相对本规则文件所在目录, 命令行 -o 可覆盖。留空为 output/&lt;主表文件名&gt;_更新后.xlsx</t>
         </is>
       </c>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="5" t="n"/>
     </row>
     <row r="4"/>
-    <row r="5">
+    <row r="5" ht="32" customHeight="1">
       <c r="A5" s="1" t="inlineStr">
         <is>
           <t>输入表</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>下一行是列名, 之后每行声明一个输入: 名称 = 规则里的前缀; 匹配 = 主表写 主表, 其它写对齐到主表的键; 文件 = 默认文件 (命令行 -i 可覆盖)。输入表下面不要再写别的</t>
         </is>
       </c>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="5" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>匹配</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>重复键</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>文件</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>客户</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>主表</t>
         </is>
       </c>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t>客户主表.xlsx</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>被更新的表: 输出的行就是它的行。规则里引用它的列写 客户.状态; 相对路径以本规则文件所在目录为基准</t>
         </is>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>本月</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>客户编号</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>取第一条</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>本月流水.xlsx</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>参照表, 按 客户编号 对齐到主表 (多个键用逗号分隔); 引用写 本月.金额, 本月.存在 = 是否匹配到</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="C5:E5"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -664,108 +747,108 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>变量</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>定义</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>偏差率</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="9" t="inlineStr">
         <is>
           <t>abs(本月.金额 - 客户.金额) / 客户.金额</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="11" t="inlineStr">
         <is>
           <t>本月金额相对主表金额的偏差比例, 本月缺失时为空</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>距上次活跃天数</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>天数差(基准日期, 客户.上次活跃)</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="11" t="inlineStr">
         <is>
           <t>基准日期见「设置」</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n"/>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="2" t="n"/>
+      <c r="A4" s="6" t="n"/>
+      <c r="B4" s="9" t="n"/>
+      <c r="C4" s="11" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>内置变量</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="B5" s="9" t="n"/>
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>客户.&lt;列名&gt;  本月.&lt;列名&gt;  本月.存在(参照表是否匹配到)  基准日期</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>连接词</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n"/>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="B6" s="9" t="n"/>
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>且 / 或 / 非 (也认 and / or / not), 两侧留空格; 可用括号分组</t>
         </is>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>空值</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="B7" s="9" t="n"/>
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>x == 空 / x != 空 判空 (也认 为空(x) / 非空(x)); 空 只能和 == / != 搭配</t>
         </is>
       </c>
     </row>
     <row r="8" ht="47" customHeight="1">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>可用函数</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n"/>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>abs  round  天数差(晚, 早)  非空(x)  为空(x)  属于(x, 值1, ...)  包含 / 不包含 / 开头是 / 开头不是 / 结尾是 / 结尾不是 (x, 文本1, ...)  拼接(a, b, ...)  数字(x)  如果(条件, 真值, 假值)</t>
         </is>
@@ -803,621 +886,636 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>命中策略</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>优先级</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>多条规则同时命中时, 每个输出列取优先级数字最小的那条; 输出格填 - 表示不改; 同一行各条件之间是 AND, 相邻同 ID 行是同一规则的 OR 分支</t>
         </is>
       </c>
+      <c r="D1" s="4" t="n"/>
+      <c r="E1" s="4" t="n"/>
+      <c r="F1" s="4" t="n"/>
+      <c r="G1" s="4" t="n"/>
+      <c r="H1" s="4" t="n"/>
+      <c r="I1" s="4" t="n"/>
+      <c r="J1" s="4" t="n"/>
+      <c r="K1" s="4" t="n"/>
+      <c r="L1" s="4" t="n"/>
+      <c r="M1" s="4" t="n"/>
+      <c r="N1" s="4" t="n"/>
+      <c r="O1" s="5" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>规则ID</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>优先级</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="D2" s="13" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="E2" s="13" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="F2" s="8" t="inlineStr">
+      <c r="F2" s="13" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="H2" s="8" t="inlineStr">
+      <c r="H2" s="13" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="I2" s="8" t="inlineStr">
+      <c r="I2" s="13" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="J2" s="9" t="inlineStr">
+      <c r="J2" s="14" t="inlineStr">
         <is>
           <t>输出</t>
         </is>
       </c>
-      <c r="K2" s="9" t="inlineStr">
+      <c r="K2" s="14" t="inlineStr">
         <is>
           <t>输出</t>
         </is>
       </c>
-      <c r="L2" s="9" t="inlineStr">
+      <c r="L2" s="14" t="inlineStr">
         <is>
           <t>输出</t>
         </is>
       </c>
-      <c r="M2" s="9" t="inlineStr">
+      <c r="M2" s="14" t="inlineStr">
         <is>
           <t>输出</t>
         </is>
       </c>
-      <c r="N2" s="9" t="inlineStr">
+      <c r="N2" s="14" t="inlineStr">
         <is>
           <t>输出</t>
         </is>
       </c>
-      <c r="O2" s="10" t="inlineStr">
+      <c r="O2" s="15" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>规则ID</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>优先级</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>客户.状态</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>客户.等级</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>偏差率</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>本月.存在</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>距上次活跃天数</t>
         </is>
       </c>
-      <c r="H3" s="8" t="inlineStr">
+      <c r="H3" s="13" t="inlineStr">
         <is>
           <t>本月.电话</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" s="13" t="inlineStr">
         <is>
           <t>客户.电话</t>
         </is>
       </c>
-      <c r="J3" s="9" t="inlineStr">
+      <c r="J3" s="14" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="K3" s="9" t="inlineStr">
+      <c r="K3" s="14" t="inlineStr">
         <is>
           <t>电话</t>
         </is>
       </c>
-      <c r="L3" s="9" t="inlineStr">
+      <c r="L3" s="14" t="inlineStr">
         <is>
           <t>复核标记</t>
         </is>
       </c>
-      <c r="M3" s="9" t="inlineStr">
+      <c r="M3" s="14" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
-      <c r="N3" s="9" t="inlineStr">
+      <c r="N3" s="14" t="inlineStr">
         <is>
           <t>提醒</t>
         </is>
       </c>
-      <c r="O3" s="10" t="inlineStr">
+      <c r="O3" s="15" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="B4" s="11" t="n">
+      <c r="B4" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>活跃</t>
         </is>
       </c>
-      <c r="D4" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E4" s="12" t="inlineStr">
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E4" s="17" t="inlineStr">
         <is>
           <t>&gt; 0.05</t>
         </is>
       </c>
-      <c r="F4" s="12" t="inlineStr">
+      <c r="F4" s="17" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G4" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H4" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I4" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J4" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K4" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" s="13" t="inlineStr">
+      <c r="G4" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H4" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I4" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J4" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L4" s="18" t="inlineStr">
         <is>
           <t>待复核</t>
         </is>
       </c>
-      <c r="M4" s="13" t="inlineStr">
+      <c r="M4" s="18" t="inlineStr">
         <is>
           <t>金额偏差超 5%</t>
         </is>
       </c>
-      <c r="N4" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="N4" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O4" s="11" t="inlineStr">
         <is>
           <t>活跃客户金额偏差超 5% 需复核</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="B5" s="11" t="n">
+      <c r="B5" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>!= 休眠</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E5" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F5" s="12" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E5" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="17" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G5" s="12" t="inlineStr">
+      <c r="G5" s="17" t="inlineStr">
         <is>
           <t>&gt; 180</t>
         </is>
       </c>
-      <c r="H5" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I5" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J5" s="13" t="inlineStr">
+      <c r="H5" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I5" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J5" s="18" t="inlineStr">
         <is>
           <t>休眠</t>
         </is>
       </c>
-      <c r="K5" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L5" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M5" s="13" t="inlineStr">
+      <c r="K5" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L5" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M5" s="18" t="inlineStr">
         <is>
           <t>连续 6 个月无流水</t>
         </is>
       </c>
-      <c r="N5" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="N5" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O5" s="11" t="inlineStr">
         <is>
           <t>本月无流水且长期不活跃, 转休眠</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
       </c>
-      <c r="B6" s="11" t="n">
+      <c r="B6" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E6" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" s="17" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G6" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H6" s="12" t="inlineStr">
+      <c r="G6" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H6" s="17" t="inlineStr">
         <is>
           <t>!= 客户.电话</t>
         </is>
       </c>
-      <c r="I6" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J6" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K6" s="13" t="inlineStr">
+      <c r="I6" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J6" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="18" t="inlineStr">
         <is>
           <t>本月.电话</t>
         </is>
       </c>
-      <c r="L6" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M6" s="13" t="inlineStr">
+      <c r="L6" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M6" s="18" t="inlineStr">
         <is>
           <t>电话变更</t>
         </is>
       </c>
-      <c r="N6" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="N6" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O6" s="11" t="inlineStr">
         <is>
           <t>本月电话与主表不同则覆盖 (本月电话为空不算不同)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>R4</t>
         </is>
       </c>
-      <c r="B7" s="11" t="n">
+      <c r="B7" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>活跃</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>VIP, 金卡</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="17" t="inlineStr">
         <is>
           <t>[0.02..0.05]</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr">
+      <c r="F7" s="17" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G7" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H7" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I7" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J7" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K7" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L7" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M7" s="13" t="inlineStr">
+      <c r="G7" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H7" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I7" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J7" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L7" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M7" s="18" t="inlineStr">
         <is>
           <t>VIP 小幅偏差, 关注</t>
         </is>
       </c>
-      <c r="N7" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="N7" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O7" s="11" t="inlineStr">
         <is>
           <t>高等级客户小幅偏差也要留意</t>
         </is>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>R5</t>
         </is>
       </c>
-      <c r="B8" s="11" t="n">
+      <c r="B8" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E8" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G8" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H8" s="12" t="inlineStr">
+      <c r="G8" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H8" s="17" t="inlineStr">
         <is>
           <t>为空</t>
         </is>
       </c>
-      <c r="I8" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J8" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K8" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L8" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M8" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N8" s="13" t="inlineStr">
+      <c r="I8" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J8" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L8" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M8" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="18" t="inlineStr">
         <is>
           <t>电话有缺失</t>
         </is>
       </c>
-      <c r="O8" s="6" t="inlineStr">
+      <c r="O8" s="8" t="inlineStr">
         <is>
           <t>本月电话为空, 提醒补录。下一行同 ID = 同一条规则的另一个「或」分支 (YAML 里 R5 的 任一满足)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>R5</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n"/>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E9" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="12" t="inlineStr">
+      <c r="B9" s="16" t="n"/>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E9" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="17" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G9" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H9" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I9" s="12" t="inlineStr">
+      <c r="G9" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H9" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I9" s="17" t="inlineStr">
         <is>
           <t>为空</t>
         </is>
       </c>
-      <c r="J9" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K9" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L9" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M9" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N9" s="13" t="n"/>
-      <c r="O9" s="6" t="inlineStr">
+      <c r="J9" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L9" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M9" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="18" t="n"/>
+      <c r="O9" s="8" t="inlineStr">
         <is>
           <t>主表电话为空, 提醒补录。续行的优先级和输出留空 (或与首行相同)</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C1:O1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1448,568 +1546,568 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>每行一个用例: 填输入变量的值, 期望列留空表示「该列不变」。运行时先跑本表, 全部通过才处理真实数据</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>用例</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="D2" s="13" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="E2" s="13" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="F2" s="8" t="inlineStr">
+      <c r="F2" s="13" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="H2" s="8" t="inlineStr">
+      <c r="H2" s="13" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="I2" s="9" t="inlineStr">
+      <c r="I2" s="14" t="inlineStr">
         <is>
           <t>期望</t>
         </is>
       </c>
-      <c r="J2" s="9" t="inlineStr">
+      <c r="J2" s="14" t="inlineStr">
         <is>
           <t>期望</t>
         </is>
       </c>
-      <c r="K2" s="9" t="inlineStr">
+      <c r="K2" s="14" t="inlineStr">
         <is>
           <t>期望</t>
         </is>
       </c>
-      <c r="L2" s="9" t="inlineStr">
+      <c r="L2" s="14" t="inlineStr">
         <is>
           <t>期望</t>
         </is>
       </c>
-      <c r="M2" s="9" t="inlineStr">
+      <c r="M2" s="14" t="inlineStr">
         <is>
           <t>期望</t>
         </is>
       </c>
-      <c r="N2" s="10" t="inlineStr">
+      <c r="N2" s="15" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>用例</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>客户.状态</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>客户.等级</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>偏差率</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>本月.存在</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>距上次活跃天数</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>客户.电话</t>
         </is>
       </c>
-      <c r="H3" s="8" t="inlineStr">
+      <c r="H3" s="13" t="inlineStr">
         <is>
           <t>本月.电话</t>
         </is>
       </c>
-      <c r="I3" s="9" t="inlineStr">
+      <c r="I3" s="14" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="J3" s="9" t="inlineStr">
+      <c r="J3" s="14" t="inlineStr">
         <is>
           <t>电话</t>
         </is>
       </c>
-      <c r="K3" s="9" t="inlineStr">
+      <c r="K3" s="14" t="inlineStr">
         <is>
           <t>复核标记</t>
         </is>
       </c>
-      <c r="L3" s="9" t="inlineStr">
+      <c r="L3" s="14" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
-      <c r="M3" s="9" t="inlineStr">
+      <c r="M3" s="14" t="inlineStr">
         <is>
           <t>提醒</t>
         </is>
       </c>
-      <c r="N3" s="10" t="inlineStr">
+      <c r="N3" s="15" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>活跃</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="D4" s="12" t="n">
+      <c r="D4" s="17" t="n">
         <v>0.08</v>
       </c>
-      <c r="E4" s="12" t="inlineStr">
+      <c r="E4" s="17" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="F4" s="12" t="n">
+      <c r="F4" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="G4" s="12" t="inlineStr">
+      <c r="G4" s="17" t="inlineStr">
         <is>
           <t>13800000001</t>
         </is>
       </c>
-      <c r="H4" s="12" t="inlineStr">
+      <c r="H4" s="17" t="inlineStr">
         <is>
           <t>13800000001</t>
         </is>
       </c>
-      <c r="I4" s="13" t="n"/>
-      <c r="J4" s="13" t="n"/>
-      <c r="K4" s="13" t="inlineStr">
+      <c r="I4" s="18" t="n"/>
+      <c r="J4" s="18" t="n"/>
+      <c r="K4" s="18" t="inlineStr">
         <is>
           <t>待复核</t>
         </is>
       </c>
-      <c r="L4" s="13" t="inlineStr">
+      <c r="L4" s="18" t="inlineStr">
         <is>
           <t>金额偏差超 5%</t>
         </is>
       </c>
-      <c r="M4" s="13" t="n"/>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="M4" s="18" t="n"/>
+      <c r="N4" s="11" t="inlineStr">
         <is>
           <t>偏差 8% 触发 R1</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>活跃</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="D5" s="12" t="n">
+      <c r="D5" s="17" t="n">
         <v>0.03</v>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E5" s="17" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="F5" s="12" t="n">
+      <c r="F5" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="G5" s="12" t="inlineStr">
+      <c r="G5" s="17" t="inlineStr">
         <is>
           <t>13800000002</t>
         </is>
       </c>
-      <c r="H5" s="12" t="inlineStr">
+      <c r="H5" s="17" t="inlineStr">
         <is>
           <t>13800000002</t>
         </is>
       </c>
-      <c r="I5" s="13" t="n"/>
-      <c r="J5" s="13" t="n"/>
-      <c r="K5" s="13" t="n"/>
-      <c r="L5" s="13" t="n"/>
-      <c r="M5" s="13" t="n"/>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="I5" s="18" t="n"/>
+      <c r="J5" s="18" t="n"/>
+      <c r="K5" s="18" t="n"/>
+      <c r="L5" s="18" t="n"/>
+      <c r="M5" s="18" t="n"/>
+      <c r="N5" s="11" t="inlineStr">
         <is>
           <t>偏差 3% 普通客户, 什么都不发生</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>活跃</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="D6" s="12" t="n"/>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="D6" s="17" t="n"/>
+      <c r="E6" s="17" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="F6" s="17" t="n">
         <v>200</v>
       </c>
-      <c r="G6" s="12" t="inlineStr">
+      <c r="G6" s="17" t="inlineStr">
         <is>
           <t>13800000003</t>
         </is>
       </c>
-      <c r="H6" s="12" t="n"/>
-      <c r="I6" s="13" t="inlineStr">
+      <c r="H6" s="17" t="n"/>
+      <c r="I6" s="18" t="inlineStr">
         <is>
           <t>休眠</t>
         </is>
       </c>
-      <c r="J6" s="13" t="n"/>
-      <c r="K6" s="13" t="n"/>
-      <c r="L6" s="13" t="inlineStr">
+      <c r="J6" s="18" t="n"/>
+      <c r="K6" s="18" t="n"/>
+      <c r="L6" s="18" t="inlineStr">
         <is>
           <t>连续 6 个月无流水</t>
         </is>
       </c>
-      <c r="M6" s="13" t="n"/>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="M6" s="18" t="n"/>
+      <c r="N6" s="11" t="inlineStr">
         <is>
           <t>本月缺失且 200 天, 触发 R2</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>休眠</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="D7" s="12" t="n"/>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="17" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="F7" s="12" t="n">
+      <c r="F7" s="17" t="n">
         <v>400</v>
       </c>
-      <c r="G7" s="12" t="inlineStr">
+      <c r="G7" s="17" t="inlineStr">
         <is>
           <t>13800000007</t>
         </is>
       </c>
-      <c r="H7" s="12" t="n"/>
-      <c r="I7" s="13" t="n"/>
-      <c r="J7" s="13" t="n"/>
-      <c r="K7" s="13" t="n"/>
-      <c r="L7" s="13" t="n"/>
-      <c r="M7" s="13" t="n"/>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="H7" s="17" t="n"/>
+      <c r="I7" s="18" t="n"/>
+      <c r="J7" s="18" t="n"/>
+      <c r="K7" s="18" t="n"/>
+      <c r="L7" s="18" t="n"/>
+      <c r="M7" s="18" t="n"/>
+      <c r="N7" s="11" t="inlineStr">
         <is>
           <t>已休眠不重复命中 R2</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>T5</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>试用</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="D8" s="12" t="n">
+      <c r="D8" s="17" t="n">
         <v>0.3</v>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="F8" s="12" t="n">
+      <c r="F8" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="G8" s="12" t="inlineStr">
+      <c r="G8" s="17" t="inlineStr">
         <is>
           <t>13800000005</t>
         </is>
       </c>
-      <c r="H8" s="12" t="inlineStr">
+      <c r="H8" s="17" t="inlineStr">
         <is>
           <t>13900000005</t>
         </is>
       </c>
-      <c r="I8" s="13" t="n"/>
-      <c r="J8" s="13" t="inlineStr">
+      <c r="I8" s="18" t="n"/>
+      <c r="J8" s="18" t="inlineStr">
         <is>
           <t>13900000005</t>
         </is>
       </c>
-      <c r="K8" s="13" t="n"/>
-      <c r="L8" s="13" t="inlineStr">
+      <c r="K8" s="18" t="n"/>
+      <c r="L8" s="18" t="inlineStr">
         <is>
           <t>电话变更</t>
         </is>
       </c>
-      <c r="M8" s="13" t="n"/>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="M8" s="18" t="n"/>
+      <c r="N8" s="11" t="inlineStr">
         <is>
           <t>试用客户不触发 R1, 只换电话</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>T6</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>活跃</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>金卡</t>
         </is>
       </c>
-      <c r="D9" s="12" t="n">
+      <c r="D9" s="17" t="n">
         <v>0.04</v>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="F9" s="12" t="n">
+      <c r="F9" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="G9" s="12" t="inlineStr">
+      <c r="G9" s="17" t="inlineStr">
         <is>
           <t>13800000008</t>
         </is>
       </c>
-      <c r="H9" s="12" t="n"/>
-      <c r="I9" s="13" t="n"/>
-      <c r="J9" s="13" t="n"/>
-      <c r="K9" s="13" t="n"/>
-      <c r="L9" s="13" t="inlineStr">
+      <c r="H9" s="17" t="n"/>
+      <c r="I9" s="18" t="n"/>
+      <c r="J9" s="18" t="n"/>
+      <c r="K9" s="18" t="n"/>
+      <c r="L9" s="18" t="inlineStr">
         <is>
           <t>VIP 小幅偏差, 关注</t>
         </is>
       </c>
-      <c r="M9" s="13" t="inlineStr">
+      <c r="M9" s="18" t="inlineStr">
         <is>
           <t>电话有缺失</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N9" s="11" t="inlineStr">
         <is>
           <t>金卡 4% 落在 R4 区间; 本月电话空不触发 R3 但触发 R5</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>T7</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>活跃</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>VIP</t>
         </is>
       </c>
-      <c r="D10" s="12" t="n">
+      <c r="D10" s="17" t="n">
         <v>0.08</v>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="F10" s="12" t="n">
+      <c r="F10" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="G10" s="12" t="inlineStr">
+      <c r="G10" s="17" t="inlineStr">
         <is>
           <t>13800000006</t>
         </is>
       </c>
-      <c r="H10" s="12" t="inlineStr">
+      <c r="H10" s="17" t="inlineStr">
         <is>
           <t>13900000006</t>
         </is>
       </c>
-      <c r="I10" s="13" t="n"/>
-      <c r="J10" s="13" t="inlineStr">
+      <c r="I10" s="18" t="n"/>
+      <c r="J10" s="18" t="inlineStr">
         <is>
           <t>13900000006</t>
         </is>
       </c>
-      <c r="K10" s="13" t="inlineStr">
+      <c r="K10" s="18" t="inlineStr">
         <is>
           <t>待复核</t>
         </is>
       </c>
-      <c r="L10" s="13" t="inlineStr">
+      <c r="L10" s="18" t="inlineStr">
         <is>
           <t>金额偏差超 5%</t>
         </is>
       </c>
-      <c r="M10" s="13" t="n"/>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="M10" s="18" t="n"/>
+      <c r="N10" s="11" t="inlineStr">
         <is>
           <t>R1 与 R3 同时命中, 备注听优先级高的 R1</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>T8</t>
         </is>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>活跃</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="D11" s="12" t="n">
+      <c r="D11" s="17" t="n">
         <v>0.01</v>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="F11" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="G11" s="12" t="n"/>
-      <c r="H11" s="12" t="inlineStr">
+      <c r="G11" s="17" t="n"/>
+      <c r="H11" s="17" t="inlineStr">
         <is>
           <t>13800000009</t>
         </is>
       </c>
-      <c r="I11" s="13" t="n"/>
-      <c r="J11" s="13" t="n"/>
-      <c r="K11" s="13" t="n"/>
-      <c r="L11" s="13" t="n"/>
-      <c r="M11" s="13" t="inlineStr">
+      <c r="I11" s="18" t="n"/>
+      <c r="J11" s="18" t="n"/>
+      <c r="K11" s="18" t="n"/>
+      <c r="L11" s="18" t="n"/>
+      <c r="M11" s="18" t="inlineStr">
         <is>
           <t>电话有缺失</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="N11" s="11" t="inlineStr">
         <is>
           <t>主表电话空, 触发 R5 的第二个分支</t>
         </is>
